--- a/data_result/2026-05-06/astgcn.xlsx
+++ b/data_result/2026-05-06/astgcn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,65 +766,132 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>pems07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>39.2419±0.8374</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>41.7657±0.5807</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-6.43%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59.5411±1.1929</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.4850±1.0463</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.26%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23.6730±0.0844</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25.3433±0.3918</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-7.06%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>36.2481±0.1719</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>38.3934±0.5406</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-5.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>pems08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>24.3711±0.3635</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>26.8478±1.6809</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>-10.16%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>38.0544±0.3865</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>40.7271±2.0609</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-7.02%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>16.8287±0.0167</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>17.5656±0.2237</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-4.38%</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>25.3433±0.0346</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>26.2689±0.3333</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>-3.65%</t>
         </is>
